--- a/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0002T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0002T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.12743923578282</v>
+        <v>4.570708875814708</v>
       </c>
       <c r="D2" t="n">
-        <v>28.49084294027268</v>
+        <v>4.629761977794311</v>
       </c>
       <c r="E2" t="n">
-        <v>13.08679405092459</v>
+        <v>2.126604033275246</v>
       </c>
       <c r="F2" t="n">
-        <v>13.06765019010571</v>
+        <v>2.123493155892177</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.98948306742111</v>
+        <v>5.52329099845593</v>
       </c>
       <c r="D3" t="n">
-        <v>33.53621540047648</v>
+        <v>5.449635002577428</v>
       </c>
       <c r="E3" t="n">
-        <v>13.08679405092459</v>
+        <v>2.126604033275246</v>
       </c>
       <c r="F3" t="n">
-        <v>13.06765019010571</v>
+        <v>2.123493155892177</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10.95998391648972</v>
+        <v>1.780997386429579</v>
       </c>
       <c r="D4" t="n">
-        <v>11.15398579001219</v>
+        <v>1.812522690876981</v>
       </c>
       <c r="E4" t="n">
-        <v>13.08679405092459</v>
+        <v>2.126604033275246</v>
       </c>
       <c r="F4" t="n">
-        <v>13.06765019010571</v>
+        <v>2.123493155892177</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.5172383534108</v>
+        <v>2.846551232429256</v>
       </c>
       <c r="D5" t="n">
-        <v>17.78350857315622</v>
+        <v>2.889820143137885</v>
       </c>
       <c r="E5" t="n">
-        <v>13.08679405092459</v>
+        <v>2.126604033275246</v>
       </c>
       <c r="F5" t="n">
-        <v>13.06765019010571</v>
+        <v>2.123493155892177</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.64743251628207</v>
+        <v>5.142707783895837</v>
       </c>
       <c r="D6" t="n">
-        <v>32.05005174160005</v>
+        <v>5.208133408010008</v>
       </c>
       <c r="E6" t="n">
-        <v>13.08679405092459</v>
+        <v>2.126604033275246</v>
       </c>
       <c r="F6" t="n">
-        <v>13.06765019010571</v>
+        <v>2.123493155892177</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.04711501473781</v>
+        <v>4.232656189894894</v>
       </c>
       <c r="D7" t="n">
-        <v>26.09468333733013</v>
+        <v>4.240386042316146</v>
       </c>
       <c r="E7" t="n">
-        <v>13.08679405092459</v>
+        <v>2.126604033275246</v>
       </c>
       <c r="F7" t="n">
-        <v>13.06765019010571</v>
+        <v>2.123493155892177</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>55.46221976372401</v>
+        <v>9.012610711605152</v>
       </c>
       <c r="D8" t="n">
-        <v>55.70098218465603</v>
+        <v>9.051409605006604</v>
       </c>
       <c r="E8" t="n">
-        <v>13.08679405092459</v>
+        <v>2.126604033275246</v>
       </c>
       <c r="F8" t="n">
-        <v>13.06765019010571</v>
+        <v>2.123493155892177</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
